--- a/exports/trend_1d/ANGELONE_full_report.xlsx
+++ b/exports/trend_1d/ANGELONE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:U41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>10.47</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44186</v>
+        <v>44187</v>
       </c>
       <c r="H2" t="n">
-        <v>33.5</v>
+        <v>32.6</v>
       </c>
       <c r="I2" t="n">
         <v>33.00418394305318</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K2" t="n">
-        <v>41.95</v>
+        <v>38.14</v>
       </c>
       <c r="L2" t="n">
         <v>5.93</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>16.55</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44302</v>
+        <v>44305</v>
       </c>
       <c r="H3" t="n">
-        <v>32.3</v>
+        <v>33.3</v>
       </c>
       <c r="I3" t="n">
         <v>32.37696871336985</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K3" t="n">
-        <v>0.92</v>
+        <v>-2.15</v>
       </c>
       <c r="L3" t="n">
         <v>15.95</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>19.13</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44428</v>
+        <v>44431</v>
       </c>
       <c r="H4" t="n">
-        <v>118.4</v>
+        <v>107.2</v>
       </c>
       <c r="I4" t="n">
         <v>112.2836129598032</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K4" t="n">
-        <v>255.56</v>
+        <v>221.92</v>
       </c>
       <c r="L4" t="n">
         <v>9.91</v>
@@ -669,7 +716,7 @@
         <v>4.02</v>
       </c>
       <c r="N4" t="n">
-        <v>6.26</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O4" t="n">
         <v>3.1</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>26.9</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44468</v>
+        <v>44469</v>
       </c>
       <c r="H5" t="n">
-        <v>127.9</v>
+        <v>132.3</v>
       </c>
       <c r="I5" t="n">
         <v>130.0177843482252</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K5" t="n">
-        <v>-19.31</v>
+        <v>-23.41</v>
       </c>
       <c r="L5" t="n">
         <v>25.93</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>14.63</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44489</v>
+        <v>44490</v>
       </c>
       <c r="H6" t="n">
-        <v>139.8</v>
+        <v>131.3</v>
       </c>
       <c r="I6" t="n">
         <v>133.6056089712339</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6" t="n">
-        <v>5.67</v>
+        <v>-0.76</v>
       </c>
       <c r="L6" t="n">
-        <v>2.87</v>
+        <v>6.65</v>
       </c>
       <c r="M6" t="n">
         <v>0.98</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>31.73</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44566</v>
+        <v>44567</v>
       </c>
       <c r="H7" t="n">
-        <v>124.2</v>
+        <v>126.7</v>
       </c>
       <c r="I7" t="n">
         <v>124.5049068962447</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K7" t="n">
-        <v>5.41</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
         <v>11.2</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>13.52</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44602</v>
+        <v>44603</v>
       </c>
       <c r="H8" t="n">
-        <v>136.4</v>
+        <v>130.7</v>
       </c>
       <c r="I8" t="n">
         <v>131.5831261191219</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K8" t="n">
-        <v>7.66</v>
+        <v>3.16</v>
       </c>
       <c r="L8" t="n">
         <v>4.03</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>15.13</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H9" t="n">
-        <v>141.7</v>
+        <v>161.9</v>
       </c>
       <c r="I9" t="n">
         <v>143.6272468684691</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K9" t="n">
-        <v>-8.42</v>
+        <v>-23.87</v>
       </c>
       <c r="L9" t="n">
-        <v>11.17</v>
+        <v>27.93</v>
       </c>
       <c r="M9" t="n">
         <v>4.68</v>
       </c>
       <c r="N9" t="n">
-        <v>7.42</v>
+        <v>14.26</v>
       </c>
       <c r="O9" t="n">
         <v>-4.18</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>19.77</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44685</v>
+        <v>44686</v>
       </c>
       <c r="H10" t="n">
-        <v>169</v>
+        <v>158.3</v>
       </c>
       <c r="I10" t="n">
         <v>165.0149481145379</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K10" t="n">
-        <v>4.39</v>
+        <v>-2.22</v>
       </c>
       <c r="L10" t="n">
         <v>11.8</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>26.68</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44763</v>
+        <v>44764</v>
       </c>
       <c r="H11" t="n">
-        <v>138.8</v>
+        <v>144.9</v>
       </c>
       <c r="I11" t="n">
         <v>140.0283237522827</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K11" t="n">
-        <v>12.32</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L11" t="n">
         <v>9.92</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>13.59</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H12" t="n">
-        <v>149.2</v>
+        <v>138.3</v>
       </c>
       <c r="I12" t="n">
         <v>140.931356617746</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K12" t="n">
-        <v>2.97</v>
+        <v>-4.55</v>
       </c>
       <c r="L12" t="n">
         <v>14.29</v>
@@ -1125,7 +1268,7 @@
         <v>4.35</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>7.31</v>
       </c>
       <c r="O12" t="n">
         <v>4.39</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>17.13</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44838</v>
+        <v>44840</v>
       </c>
       <c r="H13" t="n">
-        <v>153.2</v>
+        <v>154</v>
       </c>
       <c r="I13" t="n">
         <v>153.6381686302925</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>-10.77</v>
+        <v>-11.35</v>
       </c>
       <c r="L13" t="n">
-        <v>12.08</v>
+        <v>13.38</v>
       </c>
       <c r="M13" t="n">
         <v>5.72</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>14.35</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44875</v>
+        <v>44876</v>
       </c>
       <c r="H14" t="n">
-        <v>147.6</v>
+        <v>143.6</v>
       </c>
       <c r="I14" t="n">
         <v>147.5309471397834</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.16</v>
+        <v>-6.75</v>
       </c>
       <c r="L14" t="n">
-        <v>4.81</v>
+        <v>7.08</v>
       </c>
       <c r="M14" t="n">
         <v>1.45</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>12.35</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44896</v>
+        <v>44897</v>
       </c>
       <c r="H15" t="n">
-        <v>161</v>
+        <v>161.9</v>
       </c>
       <c r="I15" t="n">
         <v>161.333071392222</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K15" t="n">
-        <v>-12.12</v>
+        <v>-12.74</v>
       </c>
       <c r="L15" t="n">
         <v>13.09</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>9.35</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44910</v>
+        <v>44911</v>
       </c>
       <c r="H16" t="n">
-        <v>148.7</v>
+        <v>145.9</v>
       </c>
       <c r="I16" t="n">
         <v>146.763238122664</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>-8.15</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>8.83</v>
+        <v>10.07</v>
       </c>
       <c r="M16" t="n">
         <v>1.79</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>11.1</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44987</v>
+        <v>44988</v>
       </c>
       <c r="H17" t="n">
-        <v>106.1</v>
+        <v>112.2</v>
       </c>
       <c r="I17" t="n">
         <v>111.5228325235888</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K17" t="n">
-        <v>27.28</v>
+        <v>23.1</v>
       </c>
       <c r="L17" t="n">
         <v>2.74</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>13.24</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45064</v>
+        <v>45065</v>
       </c>
       <c r="H18" t="n">
-        <v>123.3</v>
+        <v>119.6</v>
       </c>
       <c r="I18" t="n">
         <v>120.9101284822644</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K18" t="n">
-        <v>9.890000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="L18" t="n">
         <v>9.98</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>10.66</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45076</v>
+        <v>45077</v>
       </c>
       <c r="H19" t="n">
-        <v>130.1</v>
+        <v>134.6</v>
       </c>
       <c r="I19" t="n">
         <v>132.3514297027863</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K19" t="n">
-        <v>-8.779999999999999</v>
+        <v>-12.54</v>
       </c>
       <c r="L19" t="n">
-        <v>10.37</v>
+        <v>12.88</v>
       </c>
       <c r="M19" t="n">
         <v>1.33</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>11.81</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45121</v>
+        <v>45124</v>
       </c>
       <c r="H20" t="n">
-        <v>170.8</v>
+        <v>158.8</v>
       </c>
       <c r="I20" t="n">
         <v>163.5302988366016</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K20" t="n">
-        <v>26.89</v>
+        <v>17.98</v>
       </c>
       <c r="L20" t="n">
         <v>4.9</v>
       </c>
       <c r="M20" t="n">
-        <v>0.17</v>
+        <v>5.04</v>
       </c>
       <c r="N20" t="n">
-        <v>3.27</v>
+        <v>7.03</v>
       </c>
       <c r="O20" t="n">
         <v>3.46</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>13.63</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45145</v>
+        <v>45146</v>
       </c>
       <c r="H21" t="n">
-        <v>151.4</v>
+        <v>170.1</v>
       </c>
       <c r="I21" t="n">
         <v>165.0729627353379</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K21" t="n">
-        <v>4.66</v>
+        <v>-7.12</v>
       </c>
       <c r="L21" t="n">
-        <v>4.16</v>
+        <v>8.94</v>
       </c>
       <c r="M21" t="n">
         <v>1.86</v>
       </c>
       <c r="N21" t="n">
-        <v>4.39</v>
+        <v>12.35</v>
       </c>
       <c r="O21" t="n">
         <v>-7.03</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>16.44</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45306</v>
+        <v>45307</v>
       </c>
       <c r="H22" t="n">
-        <v>387.6</v>
+        <v>333</v>
       </c>
       <c r="I22" t="n">
         <v>339.3986196097059</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K22" t="n">
-        <v>127.87</v>
+        <v>95.77</v>
       </c>
       <c r="L22" t="n">
         <v>10.35</v>
       </c>
       <c r="M22" t="n">
-        <v>2.07</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>6.35</v>
+        <v>14.09</v>
       </c>
       <c r="O22" t="n">
         <v>12.35</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>6</v>
+      </c>
+      <c r="U22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>20.05</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="H23" t="n">
-        <v>272.2</v>
+        <v>297.3</v>
       </c>
       <c r="I23" t="n">
         <v>285.2063409024157</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K23" t="n">
-        <v>18.26</v>
+        <v>10.72</v>
       </c>
       <c r="L23" t="n">
         <v>8.26</v>
@@ -1752,7 +2027,7 @@
         <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>8.83</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="O23" t="n">
         <v>-14.09</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>20.83</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45415</v>
+        <v>45418</v>
       </c>
       <c r="H24" t="n">
-        <v>271.7</v>
+        <v>263.1</v>
       </c>
       <c r="I24" t="n">
         <v>266.6494876268119</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K24" t="n">
-        <v>-8.609999999999999</v>
+        <v>-11.5</v>
       </c>
       <c r="L24" t="n">
-        <v>10.73</v>
+        <v>11.87</v>
       </c>
       <c r="M24" t="n">
         <v>3.33</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>14.86</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45523</v>
+        <v>45524</v>
       </c>
       <c r="H25" t="n">
-        <v>234.1</v>
+        <v>269.7</v>
       </c>
       <c r="I25" t="n">
         <v>234.7126525343584</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K25" t="n">
-        <v>11.02</v>
+        <v>-2.51</v>
       </c>
       <c r="L25" t="n">
         <v>5.28</v>
@@ -1866,7 +2165,7 @@
         <v>7.22</v>
       </c>
       <c r="N25" t="n">
-        <v>8.380000000000001</v>
+        <v>15.21</v>
       </c>
       <c r="O25" t="n">
         <v>-3.17</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>19.75</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45608</v>
+        <v>45609</v>
       </c>
       <c r="H26" t="n">
-        <v>274</v>
+        <v>261.4</v>
       </c>
       <c r="I26" t="n">
         <v>269.8206962668762</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K26" t="n">
-        <v>1.59</v>
+        <v>-3.08</v>
       </c>
       <c r="L26" t="n">
         <v>14.16</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>17.94</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="H27" t="n">
-        <v>293.6</v>
+        <v>307.7</v>
       </c>
       <c r="I27" t="n">
         <v>307.2610179646557</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>-12.32</v>
+        <v>-17.71</v>
       </c>
       <c r="L27" t="n">
-        <v>13.58</v>
+        <v>18.09</v>
       </c>
       <c r="M27" t="n">
         <v>1.58</v>
       </c>
       <c r="N27" t="n">
-        <v>3.93</v>
+        <v>4.8</v>
       </c>
       <c r="O27" t="n">
         <v>-4.6</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>14.15</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H28" t="n">
-        <v>304.5</v>
+        <v>288.2</v>
       </c>
       <c r="I28" t="n">
         <v>304.0385853706899</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.04</v>
+        <v>-6.34</v>
       </c>
       <c r="L28" t="n">
-        <v>4.58</v>
+        <v>7.38</v>
       </c>
       <c r="M28" t="n">
         <v>1.99</v>
       </c>
       <c r="N28" t="n">
-        <v>4.78</v>
+        <v>5.35</v>
       </c>
       <c r="O28" t="n">
         <v>4.8</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>17.77</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45736</v>
+        <v>45737</v>
       </c>
       <c r="H29" t="n">
-        <v>226.3</v>
+        <v>233.7</v>
       </c>
       <c r="I29" t="n">
         <v>227.1789276473201</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K29" t="n">
-        <v>21.48</v>
+        <v>18.91</v>
       </c>
       <c r="L29" t="n">
         <v>7.04</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>15.42</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45824</v>
+        <v>45825</v>
       </c>
       <c r="H30" t="n">
-        <v>293</v>
+        <v>287.4</v>
       </c>
       <c r="I30" t="n">
         <v>290.7027091771008</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K30" t="n">
-        <v>25.37</v>
+        <v>22.98</v>
       </c>
       <c r="L30" t="n">
         <v>11.98</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>12.14</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="H31" t="n">
-        <v>226.5</v>
+        <v>230.3</v>
       </c>
       <c r="I31" t="n">
         <v>230.1358598719779</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K31" t="n">
-        <v>21.19</v>
+        <v>19.87</v>
       </c>
       <c r="L31" t="n">
         <v>4.91</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>9.06</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="H32" t="n">
-        <v>264.2</v>
+        <v>254.3</v>
       </c>
       <c r="I32" t="n">
         <v>258.5680615598292</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K32" t="n">
-        <v>14.72</v>
+        <v>10.42</v>
       </c>
       <c r="L32" t="n">
         <v>2.17</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>11.78</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="H33" t="n">
-        <v>252.5</v>
+        <v>275.2</v>
       </c>
       <c r="I33" t="n">
         <v>256.5004433664029</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K33" t="n">
-        <v>0.71</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>4.4</v>
+        <v>8.81</v>
       </c>
       <c r="M33" t="n">
-        <v>1.58</v>
+        <v>2.5</v>
       </c>
       <c r="N33" t="n">
-        <v>4</v>
+        <v>8.99</v>
       </c>
       <c r="O33" t="n">
         <v>-3.75</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>13.51</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="H34" t="n">
-        <v>254.1</v>
+        <v>231.3</v>
       </c>
       <c r="I34" t="n">
         <v>243.5733230230638</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K34" t="n">
-        <v>-7.67</v>
+        <v>-15.95</v>
       </c>
       <c r="L34" t="n">
-        <v>9.449999999999999</v>
+        <v>20.06</v>
       </c>
       <c r="M34" t="n">
         <v>1.02</v>
       </c>
       <c r="N34" t="n">
-        <v>3.95</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="O34" t="n">
         <v>8.99</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>16.98</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="H35" t="n">
-        <v>264.2</v>
+        <v>271.6</v>
       </c>
       <c r="I35" t="n">
         <v>269.5853740136097</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K35" t="n">
-        <v>-14.22</v>
+        <v>-17.42</v>
       </c>
       <c r="L35" t="n">
-        <v>16.52</v>
+        <v>17.81</v>
       </c>
       <c r="M35" t="n">
         <v>4.12</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>14.08</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="H36" t="n">
-        <v>246.5</v>
+        <v>233.2</v>
       </c>
       <c r="I36" t="n">
         <v>245.9518127639499</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K36" t="n">
-        <v>-9.24</v>
+        <v>-14.14</v>
       </c>
       <c r="L36" t="n">
-        <v>11.12</v>
+        <v>15.35</v>
       </c>
       <c r="M36" t="n">
         <v>6.23</v>
       </c>
       <c r="N36" t="n">
-        <v>4.63</v>
+        <v>5.4</v>
       </c>
       <c r="O36" t="n">
         <v>2.8</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>15.26</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="H37" t="n">
-        <v>240.85</v>
+        <v>246.05</v>
       </c>
       <c r="I37" t="n">
         <v>242.5791090510042</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.28</v>
+        <v>-5.51</v>
       </c>
       <c r="L37" t="n">
-        <v>4.82</v>
+        <v>5.88</v>
       </c>
       <c r="M37" t="n">
         <v>5.02</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>15.26</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="H38" t="n">
-        <v>321.9</v>
+        <v>312.4</v>
       </c>
       <c r="I38" t="n">
         <v>318.6033391168802</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K38" t="n">
-        <v>30.83</v>
+        <v>26.97</v>
       </c>
       <c r="L38" t="n">
         <v>3.8</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>12.39</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="H39" t="n">
-        <v>297.3</v>
+        <v>305</v>
       </c>
       <c r="I39" t="n">
         <v>304.2246809401059</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K39" t="n">
-        <v>4.83</v>
+        <v>2.37</v>
       </c>
       <c r="L39" t="n">
         <v>3.39</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>12.43</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="H40" t="n">
-        <v>291.25</v>
+        <v>279</v>
       </c>
       <c r="I40" t="n">
         <v>281.1342770838214</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.51</v>
+        <v>-8.52</v>
       </c>
       <c r="L40" t="n">
         <v>12.2</v>
@@ -2721,7 +3200,7 @@
         <v>1.33</v>
       </c>
       <c r="N40" t="n">
-        <v>4.15</v>
+        <v>4.21</v>
       </c>
       <c r="O40" t="n">
         <v>2.59</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2781,6 +3272,14 @@
       <c r="Q41" t="n">
         <v>4</v>
       </c>
+      <c r="R41" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5393,7 +5892,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54.8</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="6">
@@ -5403,7 +5902,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -5413,7 +5912,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8">
@@ -5423,7 +5922,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -5433,7 +5932,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76.5</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="10">
@@ -5443,7 +5942,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>107.6</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="11">
@@ -5483,7 +5982,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.12</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="15">
@@ -5493,7 +5992,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25.6</v>
+        <v>18.01</v>
       </c>
     </row>
     <row r="16">
@@ -5503,7 +6002,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.05</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="17">
@@ -5513,7 +6012,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>255.56</v>
+        <v>221.92</v>
       </c>
     </row>
     <row r="18">
@@ -5523,7 +6022,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>61.5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
@@ -5533,7 +6032,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.039999999999999</v>
+        <v>10.65</v>
       </c>
     </row>
     <row r="20">
@@ -5543,7 +6042,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9.91</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="21">
@@ -5553,7 +6052,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25.93</v>
+        <v>27.93</v>
       </c>
     </row>
     <row r="22">
@@ -5563,7 +6062,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -5573,7 +6072,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -5583,7 +6082,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.09</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="25">
@@ -5603,7 +6102,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6.42</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="27">
@@ -5613,7 +6112,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.32</v>
+        <v>15.21</v>
       </c>
     </row>
     <row r="28">
@@ -5623,7 +6122,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
